--- a/Documentation/WYVERN_E4_BOM_Active.xlsx
+++ b/Documentation/WYVERN_E4_BOM_Active.xlsx
@@ -22,12 +22,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="205">
   <si>
     <t xml:space="preserve">WYVERN-E - Active Procurement BOM (only items actually being bought)</t>
   </si>
   <si>
-    <t xml:space="preserve">Trimmed copy of WYVERN_E4_BOM.xlsx, 2026-08-09e. Fully regenerated to match the live Amazon cart reconciliation (Pico 2W restored qty1, EMAX servo reduced to qty1, HX711 increased to qty3, Section 10 rebuilt: TRYMAG magnets dropped for Caturledas 6x2mm-250pack, laser module/Loc-Line/SmallRig light/both mesh packs added). Contains ONLY line items with a real, nonzero cost confirmed in one of the live carts (Amazon/Adafruit/Estes/Bambu) or the custom PCB fab order. The master WYVERN_E4_BOM.xlsx remains the full historical record (including items still needed but not yet in a cart, e.g. the F15-4 flight motor and E16-4 commissioning motors - see that file before assuming procurement is complete).</t>
+    <t xml:space="preserve">Trimmed copy of WYVERN_E4_BOM.xlsx, 2026-08-09f. Fully regenerated - adds HANGLIFE heat-set insert assortment (M2-M6, 345pc, $19.99) to Section 7, confirmed in the live Amazon cart. Contains ONLY line items with a real, nonzero cost confirmed in one of the live carts (Amazon/Adafruit/Estes/Bambu) or the custom PCB fab order. The master WYVERN_E4_BOM.xlsx remains the full historical record (including items still needed but not yet in a cart, e.g. the F15-4 flight motor and E16-4 commissioning motors - see that file before assuming procurement is complete).</t>
   </si>
   <si>
     <t xml:space="preserve">1. Flight Computer &amp; Sensors</t>
@@ -247,6 +247,15 @@
   </si>
   <si>
     <t xml:space="preserve">7. Harness, connectors, prototyping &amp; assembly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HANGLIFE heat-set insert assortment M2-M6 (345 pc)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B0CS6WXQPM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-09f: confirmed in cart ($19.99). Un-zeroed from earlier NOT IN CURRENT CART flag.</t>
   </si>
   <si>
     <t xml:space="preserve">Silicone USB-C dust cover inserts (10-pk)</t>
@@ -900,7 +909,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H86"/>
+  <dimension ref="A1:H87"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1699,7 +1708,7 @@
         <v>75</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C49" s="0" t="s">
         <v>76</v>
@@ -1714,78 +1723,78 @@
         <v>1</v>
       </c>
       <c r="G49" s="0" t="n">
-        <v>1.5</v>
+        <v>19.99</v>
       </c>
       <c r="H49" s="0" t="n">
         <f aca="false">F49*G49</f>
-        <v>1.5</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="B50" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C50" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="D50" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="E50" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="F50" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="0" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H50" s="0" t="n">
+        <f aca="false">F50*G50</f>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="H50" s="0" t="n">
-        <f aca="false">SUM(H49)</f>
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="s">
-        <v>78</v>
+      <c r="H51" s="0" t="n">
+        <f aca="false">SUM(H49:H50)</f>
+        <v>21.49</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B53" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="C53" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="D53" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="E53" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="F53" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="G53" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="H53" s="0" t="s">
-        <v>10</v>
+        <v>81</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="s">
-        <v>79</v>
+        <v>3</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E54" s="0" t="s">
-        <v>81</v>
-      </c>
-      <c r="F54" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="G54" s="0" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="H54" s="0" t="n">
-        <f aca="false">F54*G54</f>
-        <v>7.9</v>
+        <v>7</v>
+      </c>
+      <c r="F54" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="G54" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="H54" s="0" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1802,7 +1811,7 @@
         <v>14</v>
       </c>
       <c r="E55" s="0" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F55" s="0" t="n">
         <v>2</v>
@@ -1817,29 +1826,29 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="B56" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C56" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="D56" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="E56" s="0" t="s">
         <v>84</v>
       </c>
-      <c r="B56" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C56" s="0" t="s">
-        <v>85</v>
-      </c>
-      <c r="D56" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E56" s="0" t="s">
-        <v>86</v>
-      </c>
       <c r="F56" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G56" s="0" t="n">
-        <v>6.79</v>
+        <v>3.95</v>
       </c>
       <c r="H56" s="0" t="n">
         <f aca="false">F56*G56</f>
-        <v>20.37</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1856,92 +1865,92 @@
         <v>14</v>
       </c>
       <c r="E57" s="0" t="s">
-        <v>37</v>
+        <v>89</v>
       </c>
       <c r="F57" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G57" s="0" t="n">
-        <v>9.99</v>
+        <v>6.79</v>
       </c>
       <c r="H57" s="0" t="n">
         <f aca="false">F57*G57</f>
-        <v>9.99</v>
+        <v>20.37</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="B58" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="C58" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="D58" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="E58" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="F58" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="0" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="H58" s="0" t="n">
+        <f aca="false">F58*G58</f>
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="H58" s="0" t="n">
-        <f aca="false">SUM(H54:H57)</f>
+      <c r="H59" s="0" t="n">
+        <f aca="false">SUM(H55:H58)</f>
         <v>46.16</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B61" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="C61" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="D61" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="E61" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="F61" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="G61" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="H61" s="0" t="s">
-        <v>10</v>
+        <v>92</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="0" t="s">
-        <v>90</v>
+        <v>3</v>
       </c>
       <c r="B62" s="0" t="s">
-        <v>91</v>
+        <v>4</v>
       </c>
       <c r="C62" s="0" t="s">
-        <v>92</v>
+        <v>5</v>
       </c>
       <c r="D62" s="0" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E62" s="0" t="s">
-        <v>93</v>
-      </c>
-      <c r="F62" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="G62" s="0" t="n">
-        <v>65</v>
-      </c>
-      <c r="H62" s="0" t="n">
-        <f aca="false">F62*G62</f>
-        <v>195</v>
+        <v>7</v>
+      </c>
+      <c r="F62" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="G62" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="H62" s="0" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="B63" s="0" t="s">
         <v>94</v>
-      </c>
-      <c r="B63" s="0" t="s">
-        <v>12</v>
       </c>
       <c r="C63" s="0" t="s">
         <v>95</v>
@@ -1950,28 +1959,28 @@
         <v>14</v>
       </c>
       <c r="E63" s="0" t="s">
-        <v>37</v>
+        <v>96</v>
       </c>
       <c r="F63" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G63" s="0" t="n">
-        <v>11.69</v>
+        <v>65</v>
       </c>
       <c r="H63" s="0" t="n">
         <f aca="false">F63*G63</f>
-        <v>11.69</v>
+        <v>195</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="0" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B64" s="0" t="s">
         <v>12</v>
       </c>
       <c r="C64" s="0" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D64" s="0" t="s">
         <v>14</v>
@@ -1983,38 +1992,38 @@
         <v>1</v>
       </c>
       <c r="G64" s="0" t="n">
-        <v>18.59</v>
+        <v>11.69</v>
       </c>
       <c r="H64" s="0" t="n">
         <f aca="false">F64*G64</f>
-        <v>18.59</v>
+        <v>11.69</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="0" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B65" s="0" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C65" s="0" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D65" s="0" t="s">
         <v>14</v>
       </c>
       <c r="E65" s="0" t="s">
-        <v>100</v>
+        <v>37</v>
       </c>
       <c r="F65" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G65" s="0" t="n">
-        <v>1.5</v>
+        <v>18.59</v>
       </c>
       <c r="H65" s="0" t="n">
         <f aca="false">F65*G65</f>
-        <v>3</v>
+        <v>18.59</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2037,11 +2046,11 @@
         <v>2</v>
       </c>
       <c r="G66" s="0" t="n">
-        <v>3.95</v>
+        <v>1.5</v>
       </c>
       <c r="H66" s="0" t="n">
         <f aca="false">F66*G66</f>
-        <v>7.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2076,7 +2085,7 @@
         <v>107</v>
       </c>
       <c r="B68" s="0" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="C68" s="0" t="s">
         <v>108</v>
@@ -2085,111 +2094,111 @@
         <v>14</v>
       </c>
       <c r="E68" s="0" t="s">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="F68" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G68" s="0" t="n">
-        <v>8.35</v>
+        <v>3.95</v>
       </c>
       <c r="H68" s="0" t="n">
         <f aca="false">F68*G68</f>
-        <v>8.35</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="0" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B69" s="0" t="s">
         <v>44</v>
       </c>
       <c r="C69" s="0" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D69" s="0" t="s">
         <v>14</v>
       </c>
       <c r="E69" s="0" t="s">
-        <v>111</v>
+        <v>37</v>
       </c>
       <c r="F69" s="0" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G69" s="0" t="n">
-        <v>9</v>
+        <v>8.35</v>
       </c>
       <c r="H69" s="0" t="n">
         <f aca="false">F69*G69</f>
-        <v>36</v>
+        <v>8.35</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="B70" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="C70" s="0" t="s">
+        <v>113</v>
+      </c>
+      <c r="D70" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="E70" s="0" t="s">
+        <v>114</v>
+      </c>
+      <c r="F70" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="G70" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="H70" s="0" t="n">
+        <f aca="false">F70*G70</f>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="H70" s="0" t="n">
-        <f aca="false">SUM(H62:H69)</f>
+      <c r="H71" s="0" t="n">
+        <f aca="false">SUM(H63:H70)</f>
         <v>288.43</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="0" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B73" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="C73" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="D73" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="E73" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="F73" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="G73" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="H73" s="0" t="s">
-        <v>10</v>
+        <v>115</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="0" t="s">
-        <v>113</v>
+        <v>3</v>
       </c>
       <c r="B74" s="0" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C74" s="0" t="s">
-        <v>114</v>
+        <v>5</v>
       </c>
       <c r="D74" s="0" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E74" s="0" t="s">
-        <v>115</v>
-      </c>
-      <c r="F74" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G74" s="0" t="n">
-        <v>8.99</v>
-      </c>
-      <c r="H74" s="0" t="n">
-        <f aca="false">F74*G74</f>
-        <v>8.99</v>
+        <v>7</v>
+      </c>
+      <c r="F74" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="G74" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="H74" s="0" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2212,11 +2221,11 @@
         <v>1</v>
       </c>
       <c r="G75" s="0" t="n">
-        <v>75</v>
+        <v>8.99</v>
       </c>
       <c r="H75" s="0" t="n">
         <f aca="false">F75*G75</f>
-        <v>75</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2239,11 +2248,11 @@
         <v>1</v>
       </c>
       <c r="G76" s="0" t="n">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="H76" s="0" t="n">
         <f aca="false">F76*G76</f>
-        <v>39</v>
+        <v>75</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2260,161 +2269,188 @@
         <v>14</v>
       </c>
       <c r="E77" s="0" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F77" s="0" t="n">
         <v>1</v>
       </c>
       <c r="G77" s="0" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="H77" s="0" t="n">
         <f aca="false">F77*G77</f>
-        <v>25</v>
+        <v>39</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="0" t="s">
+        <v>125</v>
+      </c>
+      <c r="B78" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="C78" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="D78" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="E78" s="0" t="s">
         <v>124</v>
       </c>
-      <c r="B78" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C78" s="0" t="s">
-        <v>125</v>
-      </c>
-      <c r="D78" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E78" s="0" t="s">
-        <v>121</v>
-      </c>
       <c r="F78" s="0" t="n">
         <v>1</v>
       </c>
       <c r="G78" s="0" t="n">
-        <v>35.99</v>
+        <v>25</v>
       </c>
       <c r="H78" s="0" t="n">
         <f aca="false">F78*G78</f>
-        <v>35.99</v>
+        <v>25</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="0" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B79" s="0" t="s">
         <v>12</v>
       </c>
       <c r="C79" s="0" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D79" s="0" t="s">
         <v>14</v>
       </c>
       <c r="E79" s="0" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F79" s="0" t="n">
         <v>1</v>
       </c>
       <c r="G79" s="0" t="n">
-        <v>7.99</v>
+        <v>35.99</v>
       </c>
       <c r="H79" s="0" t="n">
         <f aca="false">F79*G79</f>
-        <v>7.99</v>
+        <v>35.99</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="0" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B80" s="0" t="s">
         <v>12</v>
       </c>
       <c r="C80" s="0" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D80" s="0" t="s">
         <v>14</v>
       </c>
       <c r="E80" s="0" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F80" s="0" t="n">
         <v>1</v>
       </c>
       <c r="G80" s="0" t="n">
-        <v>15.99</v>
+        <v>7.99</v>
       </c>
       <c r="H80" s="0" t="n">
         <f aca="false">F80*G80</f>
-        <v>15.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="0" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B81" s="0" t="s">
         <v>12</v>
       </c>
       <c r="C81" s="0" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D81" s="0" t="s">
         <v>14</v>
       </c>
       <c r="E81" s="0" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="F81" s="0" t="n">
         <v>1</v>
       </c>
       <c r="G81" s="0" t="n">
-        <v>9.99</v>
+        <v>15.99</v>
       </c>
       <c r="H81" s="0" t="n">
         <f aca="false">F81*G81</f>
-        <v>9.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="0" t="s">
+        <v>133</v>
+      </c>
+      <c r="B82" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="C82" s="0" t="s">
+        <v>134</v>
+      </c>
+      <c r="D82" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="E82" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="F82" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="0" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="H82" s="0" t="n">
+        <f aca="false">F82*G82</f>
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="H82" s="0" t="n">
-        <f aca="false">SUM(H74:H81)</f>
+      <c r="H83" s="0" t="n">
+        <f aca="false">SUM(H75:H82)</f>
         <v>217.95</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="0" t="s">
-        <v>133</v>
-      </c>
-      <c r="H84" s="0" t="n">
-        <f aca="false">H9+H15+H23+H30+H36+H45+H50+H58+H70+H82</f>
-        <v>1181.59</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="0" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H85" s="0" t="n">
+        <f aca="false">H9+H15+H23+H30+H36+H45+H51+H59+H71+H83</f>
+        <v>1201.58</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="0" t="s">
+        <v>137</v>
+      </c>
+      <c r="H86" s="0" t="n">
         <f aca="false">-39.6</f>
         <v>-39.6</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="0" t="s">
-        <v>135</v>
-      </c>
-      <c r="H86" s="0" t="n">
-        <f aca="false">H84+H85</f>
-        <v>1141.99</v>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="H87" s="0" t="n">
+        <f aca="false">H85+H86</f>
+        <v>1161.98</v>
       </c>
     </row>
   </sheetData>
@@ -2438,7 +2474,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2461,7 +2497,7 @@
         <v>8</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="H3" s="0" t="s">
         <v>10</v>
@@ -2469,13 +2505,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B4" s="0" t="s">
         <v>64</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D4" s="0" t="s">
         <v>6</v>
@@ -2493,13 +2529,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B5" s="0" t="s">
         <v>64</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D5" s="0" t="s">
         <v>6</v>
@@ -2517,13 +2553,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B6" s="0" t="s">
         <v>64</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D6" s="0" t="s">
         <v>6</v>
@@ -2541,19 +2577,19 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B7" s="0" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D7" s="0" t="s">
         <v>6</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F7" s="0" t="n">
         <v>3</v>
@@ -2568,19 +2604,19 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B8" s="0" t="s">
         <v>12</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D8" s="0" t="s">
         <v>6</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="F8" s="0" t="n">
         <v>1</v>
@@ -2595,13 +2631,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B9" s="0" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D9" s="0" t="s">
         <v>6</v>
@@ -2619,13 +2655,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B10" s="0" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D10" s="0" t="s">
         <v>6</v>
@@ -2643,19 +2679,19 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B11" s="0" t="s">
         <v>12</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D11" s="0" t="s">
         <v>6</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F11" s="0" t="n">
         <v>1</v>
@@ -2670,13 +2706,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B12" s="0" t="s">
         <v>12</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D12" s="0" t="s">
         <v>6</v>
@@ -2694,13 +2730,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B13" s="0" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D13" s="0" t="s">
         <v>6</v>
@@ -2718,19 +2754,19 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B14" s="0" t="s">
         <v>12</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D14" s="0" t="s">
         <v>6</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F14" s="0" t="n">
         <v>1</v>
@@ -2745,13 +2781,13 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B15" s="0" t="s">
         <v>12</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D15" s="0" t="s">
         <v>6</v>
@@ -2769,19 +2805,19 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B16" s="0" t="s">
         <v>12</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D16" s="0" t="s">
         <v>6</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F16" s="0" t="n">
         <v>1</v>
@@ -2796,19 +2832,19 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B17" s="0" t="s">
         <v>12</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="D17" s="0" t="s">
         <v>6</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F17" s="0" t="n">
         <v>2</v>
@@ -2823,19 +2859,19 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B18" s="0" t="s">
         <v>17</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D18" s="0" t="s">
         <v>6</v>
       </c>
       <c r="E18" s="0" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F18" s="0" t="n">
         <v>2</v>
@@ -2850,19 +2886,19 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D19" s="0" t="s">
         <v>6</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F19" s="0" t="n">
         <v>1</v>
@@ -2877,19 +2913,19 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D20" s="0" t="s">
         <v>6</v>
       </c>
       <c r="E20" s="0" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="F20" s="0" t="n">
         <v>4</v>
@@ -2904,19 +2940,19 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B21" s="0" t="s">
         <v>12</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D21" s="0" t="s">
         <v>6</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F21" s="0" t="n">
         <v>3</v>
@@ -2931,19 +2967,19 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B22" s="0" t="s">
         <v>12</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D22" s="0" t="s">
         <v>6</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F22" s="0" t="n">
         <v>1</v>
@@ -2958,19 +2994,19 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B23" s="0" t="s">
         <v>17</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D23" s="0" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F23" s="0" t="n">
         <v>1</v>
@@ -2985,19 +3021,19 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B24" s="0" t="s">
         <v>17</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="D24" s="0" t="s">
         <v>6</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="F24" s="0" t="n">
         <v>6</v>
@@ -3012,19 +3048,19 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B25" s="0" t="s">
         <v>17</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D25" s="0" t="s">
         <v>6</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="F25" s="0" t="n">
         <v>1</v>
@@ -3039,19 +3075,19 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B26" s="0" t="s">
         <v>17</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D26" s="0" t="s">
         <v>6</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="F26" s="0" t="n">
         <v>6</v>
@@ -3066,7 +3102,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="H27" s="0" t="n">
         <f aca="false">SUM(H4:H26)</f>
@@ -3094,7 +3130,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3156,67 +3192,67 @@
         <v>74</v>
       </c>
       <c r="B9" s="0" t="n">
-        <f aca="false">BOM!H50</f>
-        <v>1.5</v>
+        <f aca="false">BOM!H51</f>
+        <v>21.49</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B10" s="0" t="n">
-        <f aca="false">BOM!H58</f>
+        <f aca="false">BOM!H59</f>
         <v>46.16</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B11" s="0" t="n">
-        <f aca="false">BOM!H70</f>
+        <f aca="false">BOM!H71</f>
         <v>288.43</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B12" s="0" t="n">
-        <f aca="false">BOM!H82</f>
+        <f aca="false">BOM!H83</f>
         <v>217.95</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B14" s="0" t="n">
-        <f aca="false">BOM!H84</f>
-        <v>1181.59</v>
+        <f aca="false">BOM!H85</f>
+        <v>1201.58</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B15" s="0" t="n">
-        <f aca="false">BOM!H85</f>
+        <f aca="false">BOM!H86</f>
         <v>-39.6</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B16" s="0" t="n">
-        <f aca="false">BOM!H86</f>
-        <v>1141.99</v>
+        <f aca="false">BOM!H87</f>
+        <v>1161.98</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B18" s="0" t="n">
         <f aca="false">'Already Acquired'!H27</f>
@@ -3225,11 +3261,11 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B19" s="0" t="n">
         <f aca="false">B16+B18</f>
-        <v>1621.26</v>
+        <v>1641.25</v>
       </c>
     </row>
   </sheetData>

--- a/Documentation/WYVERN_E4_BOM_Active.xlsx
+++ b/Documentation/WYVERN_E4_BOM_Active.xlsx
@@ -312,7 +312,7 @@
     <t xml:space="preserve">RP2350B flight computer board</t>
   </si>
   <si>
-    <t xml:space="preserve">DFM-reviewed Gerber submission (soldermask/silkscreen/SMT placement flags addressed). $195 total for 3 fabricated boards.</t>
+    <t xml:space="preserve">DFM-reviewed Gerber submission (soldermask/silkscreen/SMT placement flags addressed). $200 total for 3 fabricated boards (updated 2026-08-10, was $195); one of the three is earmarked for the ground servo TVC test stand rather than flight/spare use.</t>
   </si>
   <si>
     <t xml:space="preserve">eMagTech F-F servo extension cable 10cm (10-pk)</t>
@@ -712,8 +712,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -912,1545 +916,1545 @@
   <dimension ref="A1:H87"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="0" t="s">
+      <c r="D5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="0" t="s">
+      <c r="F5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="0" t="s">
+      <c r="G5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H5" s="0" t="s">
+      <c r="H5" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="0" t="s">
+      <c r="B6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="0" t="s">
+      <c r="D6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="0" t="n">
+      <c r="F6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1" t="n">
         <v>16.31</v>
       </c>
-      <c r="H6" s="0" t="n">
+      <c r="H6" s="1" t="n">
         <f aca="false">F6*G6</f>
         <v>16.31</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="0" t="s">
+      <c r="D7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="0" t="n">
+      <c r="F7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1" t="n">
         <v>29.5</v>
       </c>
-      <c r="H7" s="0" t="n">
+      <c r="H7" s="1" t="n">
         <f aca="false">F7*G7</f>
         <v>29.5</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="0" t="s">
+      <c r="B8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="0" t="s">
+      <c r="D8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F8" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="0" t="n">
+      <c r="F8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1" t="n">
         <v>67.99</v>
       </c>
-      <c r="H8" s="0" t="n">
+      <c r="H8" s="1" t="n">
         <f aca="false">F8*G8</f>
         <v>67.99</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H9" s="0" t="n">
+      <c r="H9" s="1" t="n">
         <f aca="false">SUM(H6:H8)</f>
         <v>113.8</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D12" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="E12" s="0" t="s">
+      <c r="D12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F12" s="0" t="s">
+      <c r="F12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="0" t="s">
+      <c r="G12" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H12" s="0" t="s">
+      <c r="H12" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="0" t="s">
+      <c r="B13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="0" t="s">
+      <c r="D13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F13" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="0" t="n">
+      <c r="F13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="1" t="n">
         <v>14.25</v>
       </c>
-      <c r="H13" s="0" t="n">
+      <c r="H13" s="1" t="n">
         <f aca="false">F13*G13</f>
         <v>14.25</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="0" t="s">
+      <c r="B14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="0" t="s">
+      <c r="D14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F14" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" s="0" t="n">
+      <c r="F14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="1" t="n">
         <v>15.63</v>
       </c>
-      <c r="H14" s="0" t="n">
+      <c r="H14" s="1" t="n">
         <f aca="false">F14*G14</f>
         <v>15.63</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H15" s="0" t="n">
+      <c r="H15" s="1" t="n">
         <f aca="false">SUM(H13:H14)</f>
         <v>29.88</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="0" t="s">
+      <c r="C18" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D18" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="E18" s="0" t="s">
+      <c r="D18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F18" s="0" t="s">
+      <c r="F18" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G18" s="0" t="s">
+      <c r="G18" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H18" s="0" t="s">
+      <c r="H18" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B19" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" s="0" t="s">
+      <c r="B19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D19" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E19" s="0" t="s">
+      <c r="D19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F19" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" s="0" t="n">
+      <c r="F19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="1" t="n">
         <v>39.99</v>
       </c>
-      <c r="H19" s="0" t="n">
+      <c r="H19" s="1" t="n">
         <f aca="false">F19*G19</f>
         <v>39.99</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" s="0" t="s">
+      <c r="B20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D20" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E20" s="0" t="s">
+      <c r="D20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F20" s="0" t="n">
+      <c r="F20" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G20" s="0" t="n">
+      <c r="G20" s="1" t="n">
         <v>6.99</v>
       </c>
-      <c r="H20" s="0" t="n">
+      <c r="H20" s="1" t="n">
         <f aca="false">F20*G20</f>
         <v>13.98</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" s="0" t="s">
+      <c r="B21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D21" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E21" s="0" t="s">
+      <c r="D21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F21" s="0" t="n">
+      <c r="F21" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G21" s="0" t="n">
+      <c r="G21" s="1" t="n">
         <v>12.99</v>
       </c>
-      <c r="H21" s="0" t="n">
+      <c r="H21" s="1" t="n">
         <f aca="false">F21*G21</f>
         <v>25.98</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C22" s="0" t="s">
+      <c r="B22" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D22" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E22" s="0" t="s">
+      <c r="D22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F22" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" s="0" t="n">
+      <c r="F22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="1" t="n">
         <v>6.99</v>
       </c>
-      <c r="H22" s="0" t="n">
+      <c r="H22" s="1" t="n">
         <f aca="false">F22*G22</f>
         <v>6.99</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H23" s="0" t="n">
+      <c r="H23" s="1" t="n">
         <f aca="false">SUM(H19:H22)</f>
         <v>86.94</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B26" s="0" t="s">
+      <c r="B26" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C26" s="0" t="s">
+      <c r="C26" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D26" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="E26" s="0" t="s">
+      <c r="D26" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F26" s="0" t="s">
+      <c r="F26" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G26" s="0" t="s">
+      <c r="G26" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H26" s="0" t="s">
+      <c r="H26" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="0" t="s">
+      <c r="B27" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C27" s="0" t="s">
+      <c r="C27" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D27" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E27" s="0" t="s">
+      <c r="D27" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F27" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" s="0" t="n">
+      <c r="F27" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="1" t="n">
         <v>9.23</v>
       </c>
-      <c r="H27" s="0" t="n">
+      <c r="H27" s="1" t="n">
         <f aca="false">F27*G27</f>
         <v>9.23</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B28" s="0" t="s">
+      <c r="B28" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C28" s="0" t="s">
+      <c r="C28" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D28" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="F28" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" s="0" t="n">
+      <c r="D28" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F28" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="H28" s="0" t="n">
+      <c r="H28" s="1" t="n">
         <f aca="false">F28*G28</f>
         <v>9</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B29" s="0" t="s">
+      <c r="B29" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C29" s="0" t="s">
+      <c r="C29" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D29" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E29" s="0" t="s">
+      <c r="D29" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F29" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" s="0" t="n">
+      <c r="F29" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="1" t="n">
         <v>5.4</v>
       </c>
-      <c r="H29" s="0" t="n">
+      <c r="H29" s="1" t="n">
         <f aca="false">F29*G29</f>
         <v>5.4</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H30" s="0" t="n">
+      <c r="H30" s="1" t="n">
         <f aca="false">SUM(H27:H29)</f>
         <v>23.63</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B33" s="0" t="s">
+      <c r="B33" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C33" s="0" t="s">
+      <c r="C33" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D33" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="E33" s="0" t="s">
+      <c r="D33" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F33" s="0" t="s">
+      <c r="F33" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G33" s="0" t="s">
+      <c r="G33" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H33" s="0" t="s">
+      <c r="H33" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B34" s="0" t="s">
+      <c r="B34" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C34" s="0" t="s">
+      <c r="C34" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D34" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E34" s="0" t="s">
+      <c r="D34" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F34" s="0" t="n">
+      <c r="F34" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="G34" s="0" t="n">
+      <c r="G34" s="1" t="n">
         <v>33.99</v>
       </c>
-      <c r="H34" s="0" t="n">
+      <c r="H34" s="1" t="n">
         <f aca="false">F34*G34</f>
         <v>169.95</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B35" s="0" t="s">
+      <c r="B35" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C35" s="0" t="s">
+      <c r="C35" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D35" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E35" s="0" t="s">
+      <c r="D35" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F35" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" s="0" t="n">
+      <c r="F35" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="1" t="n">
         <v>39.6</v>
       </c>
-      <c r="H35" s="0" t="n">
+      <c r="H35" s="1" t="n">
         <f aca="false">F35*G35</f>
         <v>39.6</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H36" s="0" t="n">
+      <c r="H36" s="1" t="n">
         <f aca="false">SUM(H34:H35)</f>
         <v>209.55</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B39" s="0" t="s">
+      <c r="B39" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C39" s="0" t="s">
+      <c r="C39" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D39" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="E39" s="0" t="s">
+      <c r="D39" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F39" s="0" t="s">
+      <c r="F39" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G39" s="0" t="s">
+      <c r="G39" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H39" s="0" t="s">
+      <c r="H39" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B40" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C40" s="0" t="s">
+      <c r="B40" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D40" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E40" s="0" t="s">
+      <c r="D40" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F40" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" s="0" t="n">
+      <c r="F40" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="1" t="n">
         <v>49.99</v>
       </c>
-      <c r="H40" s="0" t="n">
+      <c r="H40" s="1" t="n">
         <f aca="false">F40*G40</f>
         <v>49.99</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B41" s="0" t="s">
+      <c r="B41" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C41" s="0" t="s">
+      <c r="C41" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D41" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E41" s="0" t="s">
+      <c r="D41" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E41" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="F41" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" s="0" t="n">
+      <c r="F41" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="1" t="n">
         <v>49.99</v>
       </c>
-      <c r="H41" s="0" t="n">
+      <c r="H41" s="1" t="n">
         <f aca="false">F41*G41</f>
         <v>49.99</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B42" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C42" s="0" t="s">
+      <c r="B42" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D42" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E42" s="0" t="s">
+      <c r="D42" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E42" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F42" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" s="0" t="n">
+      <c r="F42" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="1" t="n">
         <v>16.99</v>
       </c>
-      <c r="H42" s="0" t="n">
+      <c r="H42" s="1" t="n">
         <f aca="false">F42*G42</f>
         <v>16.99</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="s">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B43" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C43" s="0" t="s">
+      <c r="B43" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D43" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E43" s="0" t="s">
+      <c r="D43" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E43" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F43" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" s="0" t="n">
+      <c r="F43" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="1" t="n">
         <v>28.79</v>
       </c>
-      <c r="H43" s="0" t="n">
+      <c r="H43" s="1" t="n">
         <f aca="false">F43*G43</f>
         <v>28.79</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B44" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C44" s="0" t="s">
+      <c r="B44" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D44" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E44" s="0" t="s">
+      <c r="D44" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E44" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="F44" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" s="0" t="n">
+      <c r="F44" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="1" t="n">
         <v>17.99</v>
       </c>
-      <c r="H44" s="0" t="n">
+      <c r="H44" s="1" t="n">
         <f aca="false">F44*G44</f>
         <v>17.99</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="s">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H45" s="0" t="n">
+      <c r="H45" s="1" t="n">
         <f aca="false">SUM(H40:H44)</f>
         <v>163.75</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="s">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="s">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B48" s="0" t="s">
+      <c r="B48" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C48" s="0" t="s">
+      <c r="C48" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D48" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="E48" s="0" t="s">
+      <c r="D48" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E48" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F48" s="0" t="s">
+      <c r="F48" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G48" s="0" t="s">
+      <c r="G48" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H48" s="0" t="s">
+      <c r="H48" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="s">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B49" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C49" s="0" t="s">
+      <c r="B49" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C49" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="D49" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E49" s="0" t="s">
+      <c r="D49" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E49" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="F49" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G49" s="0" t="n">
+      <c r="F49" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="1" t="n">
         <v>19.99</v>
       </c>
-      <c r="H49" s="0" t="n">
+      <c r="H49" s="1" t="n">
         <f aca="false">F49*G49</f>
         <v>19.99</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="s">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B50" s="0" t="s">
+      <c r="B50" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C50" s="0" t="s">
+      <c r="C50" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D50" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E50" s="0" t="s">
+      <c r="D50" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E50" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="F50" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G50" s="0" t="n">
+      <c r="F50" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="1" t="n">
         <v>1.5</v>
       </c>
-      <c r="H50" s="0" t="n">
+      <c r="H50" s="1" t="n">
         <f aca="false">F50*G50</f>
         <v>1.5</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="s">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H51" s="0" t="n">
+      <c r="H51" s="1" t="n">
         <f aca="false">SUM(H49:H50)</f>
         <v>21.49</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0" t="s">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0" t="s">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B54" s="0" t="s">
+      <c r="B54" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C54" s="0" t="s">
+      <c r="C54" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D54" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="E54" s="0" t="s">
+      <c r="D54" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E54" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F54" s="0" t="s">
+      <c r="F54" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G54" s="0" t="s">
+      <c r="G54" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H54" s="0" t="s">
+      <c r="H54" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0" t="s">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B55" s="0" t="s">
+      <c r="B55" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C55" s="0" t="s">
+      <c r="C55" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D55" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E55" s="0" t="s">
+      <c r="D55" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E55" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F55" s="0" t="n">
+      <c r="F55" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G55" s="0" t="n">
+      <c r="G55" s="1" t="n">
         <v>3.95</v>
       </c>
-      <c r="H55" s="0" t="n">
+      <c r="H55" s="1" t="n">
         <f aca="false">F55*G55</f>
         <v>7.9</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="0" t="s">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B56" s="0" t="s">
+      <c r="B56" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C56" s="0" t="s">
+      <c r="C56" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D56" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E56" s="0" t="s">
+      <c r="D56" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E56" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F56" s="0" t="n">
+      <c r="F56" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G56" s="0" t="n">
+      <c r="G56" s="1" t="n">
         <v>3.95</v>
       </c>
-      <c r="H56" s="0" t="n">
+      <c r="H56" s="1" t="n">
         <f aca="false">F56*G56</f>
         <v>7.9</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="s">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B57" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C57" s="0" t="s">
+      <c r="B57" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C57" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D57" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E57" s="0" t="s">
+      <c r="D57" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E57" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="F57" s="0" t="n">
+      <c r="F57" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="G57" s="0" t="n">
+      <c r="G57" s="1" t="n">
         <v>6.79</v>
       </c>
-      <c r="H57" s="0" t="n">
+      <c r="H57" s="1" t="n">
         <f aca="false">F57*G57</f>
         <v>20.37</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0" t="s">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B58" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C58" s="0" t="s">
+      <c r="B58" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C58" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D58" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E58" s="0" t="s">
+      <c r="D58" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E58" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F58" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G58" s="0" t="n">
+      <c r="F58" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="1" t="n">
         <v>9.99</v>
       </c>
-      <c r="H58" s="0" t="n">
+      <c r="H58" s="1" t="n">
         <f aca="false">F58*G58</f>
         <v>9.99</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="s">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H59" s="0" t="n">
+      <c r="H59" s="1" t="n">
         <f aca="false">SUM(H55:H58)</f>
         <v>46.16</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="s">
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0" t="s">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B62" s="0" t="s">
+      <c r="B62" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C62" s="0" t="s">
+      <c r="C62" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D62" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="E62" s="0" t="s">
+      <c r="D62" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E62" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F62" s="0" t="s">
+      <c r="F62" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G62" s="0" t="s">
+      <c r="G62" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H62" s="0" t="s">
+      <c r="H62" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="0" t="s">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B63" s="0" t="s">
+      <c r="B63" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C63" s="0" t="s">
+      <c r="C63" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="D63" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E63" s="0" t="s">
+      <c r="D63" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E63" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="F63" s="0" t="n">
+      <c r="F63" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="G63" s="0" t="n">
-        <v>65</v>
-      </c>
-      <c r="H63" s="0" t="n">
+      <c r="G63" s="1" t="n">
+        <v>66.6666666666667</v>
+      </c>
+      <c r="H63" s="1" t="n">
         <f aca="false">F63*G63</f>
-        <v>195</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B64" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C64" s="0" t="s">
+      <c r="B64" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C64" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D64" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E64" s="0" t="s">
+      <c r="D64" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E64" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F64" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G64" s="0" t="n">
+      <c r="F64" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" s="1" t="n">
         <v>11.69</v>
       </c>
-      <c r="H64" s="0" t="n">
+      <c r="H64" s="1" t="n">
         <f aca="false">F64*G64</f>
         <v>11.69</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="0" t="s">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B65" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C65" s="0" t="s">
+      <c r="B65" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C65" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D65" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E65" s="0" t="s">
+      <c r="D65" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E65" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F65" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G65" s="0" t="n">
+      <c r="F65" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="1" t="n">
         <v>18.59</v>
       </c>
-      <c r="H65" s="0" t="n">
+      <c r="H65" s="1" t="n">
         <f aca="false">F65*G65</f>
         <v>18.59</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="0" t="s">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B66" s="0" t="s">
+      <c r="B66" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C66" s="0" t="s">
+      <c r="C66" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D66" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E66" s="0" t="s">
+      <c r="D66" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E66" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F66" s="0" t="n">
+      <c r="F66" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G66" s="0" t="n">
+      <c r="G66" s="1" t="n">
         <v>1.5</v>
       </c>
-      <c r="H66" s="0" t="n">
+      <c r="H66" s="1" t="n">
         <f aca="false">F66*G66</f>
         <v>3</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="0" t="s">
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B67" s="0" t="s">
+      <c r="B67" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C67" s="0" t="s">
+      <c r="C67" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="D67" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E67" s="0" t="s">
+      <c r="D67" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E67" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="F67" s="0" t="n">
+      <c r="F67" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G67" s="0" t="n">
+      <c r="G67" s="1" t="n">
         <v>3.95</v>
       </c>
-      <c r="H67" s="0" t="n">
+      <c r="H67" s="1" t="n">
         <f aca="false">F67*G67</f>
         <v>7.9</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="0" t="s">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B68" s="0" t="s">
+      <c r="B68" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C68" s="0" t="s">
+      <c r="C68" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="D68" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E68" s="0" t="s">
+      <c r="D68" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E68" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="F68" s="0" t="n">
+      <c r="F68" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G68" s="0" t="n">
+      <c r="G68" s="1" t="n">
         <v>3.95</v>
       </c>
-      <c r="H68" s="0" t="n">
+      <c r="H68" s="1" t="n">
         <f aca="false">F68*G68</f>
         <v>7.9</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="0" t="s">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B69" s="0" t="s">
+      <c r="B69" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C69" s="0" t="s">
+      <c r="C69" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D69" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E69" s="0" t="s">
+      <c r="D69" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E69" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F69" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G69" s="0" t="n">
+      <c r="F69" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="1" t="n">
         <v>8.35</v>
       </c>
-      <c r="H69" s="0" t="n">
+      <c r="H69" s="1" t="n">
         <f aca="false">F69*G69</f>
         <v>8.35</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="0" t="s">
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B70" s="0" t="s">
+      <c r="B70" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C70" s="0" t="s">
+      <c r="C70" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D70" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E70" s="0" t="s">
+      <c r="D70" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E70" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="F70" s="0" t="n">
+      <c r="F70" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="G70" s="0" t="n">
+      <c r="G70" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="H70" s="0" t="n">
+      <c r="H70" s="1" t="n">
         <f aca="false">F70*G70</f>
         <v>36</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="0" t="s">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H71" s="0" t="n">
+      <c r="H71" s="1" t="n">
         <f aca="false">SUM(H63:H70)</f>
-        <v>288.43</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="0" t="s">
+        <v>293.43</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="1" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="0" t="s">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B74" s="0" t="s">
+      <c r="B74" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C74" s="0" t="s">
+      <c r="C74" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D74" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="E74" s="0" t="s">
+      <c r="D74" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E74" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F74" s="0" t="s">
+      <c r="F74" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G74" s="0" t="s">
+      <c r="G74" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H74" s="0" t="s">
+      <c r="H74" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="0" t="s">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B75" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C75" s="0" t="s">
+      <c r="B75" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C75" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="D75" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E75" s="0" t="s">
+      <c r="D75" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E75" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="F75" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G75" s="0" t="n">
+      <c r="F75" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="1" t="n">
         <v>8.99</v>
       </c>
-      <c r="H75" s="0" t="n">
+      <c r="H75" s="1" t="n">
         <f aca="false">F75*G75</f>
         <v>8.99</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="0" t="s">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B76" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C76" s="0" t="s">
+      <c r="B76" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C76" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="D76" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E76" s="0" t="s">
+      <c r="D76" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E76" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="F76" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G76" s="0" t="n">
+      <c r="F76" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="1" t="n">
         <v>75</v>
       </c>
-      <c r="H76" s="0" t="n">
+      <c r="H76" s="1" t="n">
         <f aca="false">F76*G76</f>
         <v>75</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="0" t="s">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B77" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C77" s="0" t="s">
+      <c r="B77" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C77" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D77" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E77" s="0" t="s">
+      <c r="D77" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E77" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="F77" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G77" s="0" t="n">
+      <c r="F77" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="H77" s="0" t="n">
+      <c r="H77" s="1" t="n">
         <f aca="false">F77*G77</f>
         <v>39</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="0" t="s">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B78" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C78" s="0" t="s">
+      <c r="B78" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C78" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D78" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E78" s="0" t="s">
+      <c r="D78" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E78" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="F78" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G78" s="0" t="n">
+      <c r="F78" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="H78" s="0" t="n">
+      <c r="H78" s="1" t="n">
         <f aca="false">F78*G78</f>
         <v>25</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="0" t="s">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B79" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C79" s="0" t="s">
+      <c r="B79" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C79" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D79" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E79" s="0" t="s">
+      <c r="D79" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E79" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="F79" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G79" s="0" t="n">
+      <c r="F79" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="1" t="n">
         <v>35.99</v>
       </c>
-      <c r="H79" s="0" t="n">
+      <c r="H79" s="1" t="n">
         <f aca="false">F79*G79</f>
         <v>35.99</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="0" t="s">
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B80" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C80" s="0" t="s">
+      <c r="B80" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C80" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="D80" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E80" s="0" t="s">
+      <c r="D80" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E80" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="F80" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G80" s="0" t="n">
+      <c r="F80" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" s="1" t="n">
         <v>7.99</v>
       </c>
-      <c r="H80" s="0" t="n">
+      <c r="H80" s="1" t="n">
         <f aca="false">F80*G80</f>
         <v>7.99</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="0" t="s">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B81" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C81" s="0" t="s">
+      <c r="B81" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C81" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="D81" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E81" s="0" t="s">
+      <c r="D81" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E81" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="F81" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G81" s="0" t="n">
+      <c r="F81" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="1" t="n">
         <v>15.99</v>
       </c>
-      <c r="H81" s="0" t="n">
+      <c r="H81" s="1" t="n">
         <f aca="false">F81*G81</f>
         <v>15.99</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="0" t="s">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B82" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C82" s="0" t="s">
+      <c r="B82" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C82" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="D82" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E82" s="0" t="s">
+      <c r="D82" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E82" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="F82" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G82" s="0" t="n">
+      <c r="F82" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="1" t="n">
         <v>9.99</v>
       </c>
-      <c r="H82" s="0" t="n">
+      <c r="H82" s="1" t="n">
         <f aca="false">F82*G82</f>
         <v>9.99</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="0" t="s">
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H83" s="0" t="n">
+      <c r="H83" s="1" t="n">
         <f aca="false">SUM(H75:H82)</f>
         <v>217.95</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="0" t="s">
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="H85" s="0" t="n">
+      <c r="H85" s="1" t="n">
         <f aca="false">H9+H15+H23+H30+H36+H45+H51+H59+H71+H83</f>
-        <v>1201.58</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="0" t="s">
+        <v>1206.58</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="H86" s="0" t="n">
+      <c r="H86" s="1" t="n">
         <f aca="false">-39.6</f>
         <v>-39.6</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="0" t="s">
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="H87" s="0" t="n">
+      <c r="H87" s="1" t="n">
         <f aca="false">H85+H86</f>
-        <v>1161.98</v>
+        <v>1166.98</v>
       </c>
     </row>
   </sheetData>
@@ -2472,639 +2476,639 @@
   <dimension ref="A1:H27"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="0" t="s">
+      <c r="D3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="G3" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="H3" s="0" t="s">
+      <c r="H3" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="D4" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" s="0" t="n">
+      <c r="D4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G4" s="0" t="n">
+      <c r="G4" s="1" t="n">
         <v>12.795</v>
       </c>
-      <c r="H4" s="0" t="n">
+      <c r="H4" s="1" t="n">
         <f aca="false">F4*G4</f>
         <v>25.59</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="D5" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="0" t="n">
+      <c r="D5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1" t="n">
         <v>19.99</v>
       </c>
-      <c r="H5" s="0" t="n">
+      <c r="H5" s="1" t="n">
         <f aca="false">F5*G5</f>
         <v>19.99</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="D6" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="0" t="n">
+      <c r="D6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1" t="n">
         <v>19.99</v>
       </c>
-      <c r="H6" s="0" t="n">
+      <c r="H6" s="1" t="n">
         <f aca="false">F6*G6</f>
         <v>19.99</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B7" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="0" t="s">
+      <c r="B7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="D7" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" s="0" t="s">
+      <c r="D7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="F7" s="0" t="n">
+      <c r="F7" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="G7" s="0" t="n">
+      <c r="G7" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="H7" s="0" t="n">
+      <c r="H7" s="1" t="n">
         <f aca="false">F7*G7</f>
         <v>27</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B8" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="0" t="s">
+      <c r="B8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="D8" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8" s="0" t="s">
+      <c r="D8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="F8" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="0" t="n">
+      <c r="F8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="H8" s="0" t="n">
+      <c r="H8" s="1" t="n">
         <f aca="false">F8*G8</f>
         <v>25</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B9" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="0" t="s">
+      <c r="B9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="D9" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="0" t="n">
+      <c r="D9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="H9" s="0" t="n">
+      <c r="H9" s="1" t="n">
         <f aca="false">F9*G9</f>
         <v>7</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B10" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="0" t="s">
+      <c r="B10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="D10" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="H10" s="0" t="n">
+      <c r="D10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="H10" s="1" t="n">
         <f aca="false">F10*G10</f>
         <v>6</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B11" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="0" t="s">
+      <c r="B11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="D11" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" s="0" t="s">
+      <c r="D11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="F11" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="0" t="n">
+      <c r="F11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="H11" s="0" t="n">
+      <c r="H11" s="1" t="n">
         <f aca="false">F11*G11</f>
         <v>16</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B12" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="0" t="s">
+      <c r="B12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D12" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="H12" s="0" t="n">
+      <c r="D12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="H12" s="1" t="n">
         <f aca="false">F12*G12</f>
         <v>12</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="B13" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="0" t="s">
+      <c r="B13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D13" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="0" t="n">
+      <c r="D13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="H13" s="0" t="n">
+      <c r="H13" s="1" t="n">
         <f aca="false">F13*G13</f>
         <v>15</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="B14" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="0" t="s">
+      <c r="B14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="D14" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="E14" s="0" t="s">
+      <c r="D14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="F14" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" s="0" t="n">
+      <c r="F14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="H14" s="0" t="n">
+      <c r="H14" s="1" t="n">
         <f aca="false">F14*G14</f>
         <v>21</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B15" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" s="0" t="s">
+      <c r="B15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="D15" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" s="0" t="n">
+      <c r="D15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="H15" s="0" t="n">
+      <c r="H15" s="1" t="n">
         <f aca="false">F15*G15</f>
         <v>11</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B16" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" s="0" t="s">
+      <c r="B16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="D16" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="E16" s="0" t="s">
+      <c r="D16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="F16" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" s="0" t="n">
+      <c r="F16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="H16" s="0" t="n">
+      <c r="H16" s="1" t="n">
         <f aca="false">F16*G16</f>
         <v>10</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B17" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="0" t="s">
+      <c r="B17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="D17" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="E17" s="0" t="s">
+      <c r="D17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="F17" s="0" t="n">
+      <c r="F17" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G17" s="0" t="n">
+      <c r="G17" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="H17" s="0" t="n">
+      <c r="H17" s="1" t="n">
         <f aca="false">F17*G17</f>
         <v>18</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="0" t="s">
+      <c r="C18" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="D18" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="E18" s="0" t="s">
+      <c r="D18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="F18" s="0" t="n">
+      <c r="F18" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G18" s="0" t="n">
+      <c r="G18" s="1" t="n">
         <v>22.5</v>
       </c>
-      <c r="H18" s="0" t="n">
+      <c r="H18" s="1" t="n">
         <f aca="false">F18*G18</f>
         <v>45</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="C19" s="0" t="s">
+      <c r="C19" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="D19" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="E19" s="0" t="s">
+      <c r="D19" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="F19" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" s="0" t="n">
+      <c r="F19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="H19" s="0" t="n">
+      <c r="H19" s="1" t="n">
         <f aca="false">F19*G19</f>
         <v>40</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="C20" s="0" t="s">
+      <c r="C20" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="D20" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="E20" s="0" t="s">
+      <c r="D20" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="F20" s="0" t="n">
+      <c r="F20" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="G20" s="0" t="n">
+      <c r="G20" s="1" t="n">
         <v>1.6</v>
       </c>
-      <c r="H20" s="0" t="n">
+      <c r="H20" s="1" t="n">
         <f aca="false">F20*G20</f>
         <v>6.4</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B21" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" s="0" t="s">
+      <c r="B21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="D21" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="E21" s="0" t="s">
+      <c r="D21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="F21" s="0" t="n">
+      <c r="F21" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="G21" s="0" t="n">
+      <c r="G21" s="1" t="n">
         <v>11.6</v>
       </c>
-      <c r="H21" s="0" t="n">
+      <c r="H21" s="1" t="n">
         <f aca="false">F21*G21</f>
         <v>34.8</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B22" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C22" s="0" t="s">
+      <c r="B22" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="D22" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="E22" s="0" t="s">
+      <c r="D22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="F22" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" s="0" t="n">
+      <c r="F22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="H22" s="0" t="n">
+      <c r="H22" s="1" t="n">
         <f aca="false">F22*G22</f>
         <v>9</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="0" t="s">
+      <c r="C23" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="D23" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="E23" s="0" t="s">
+      <c r="D23" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="F23" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="H23" s="0" t="n">
+      <c r="F23" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="H23" s="1" t="n">
         <f aca="false">F23*G23</f>
         <v>6</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C24" s="0" t="s">
+      <c r="C24" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="D24" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="E24" s="0" t="s">
+      <c r="D24" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="F24" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="G24" s="0" t="n">
+      <c r="F24" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="G24" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="H24" s="0" t="n">
+      <c r="H24" s="1" t="n">
         <f aca="false">F24*G24</f>
         <v>90</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="B25" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C25" s="0" t="s">
+      <c r="C25" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="D25" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="E25" s="0" t="s">
+      <c r="D25" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="F25" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" s="0" t="n">
+      <c r="F25" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="H25" s="0" t="n">
+      <c r="H25" s="1" t="n">
         <f aca="false">F25*G25</f>
         <v>7</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B26" s="0" t="s">
+      <c r="B26" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C26" s="0" t="s">
+      <c r="C26" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="D26" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="E26" s="0" t="s">
+      <c r="D26" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="F26" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="G26" s="0" t="n">
+      <c r="F26" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="G26" s="1" t="n">
         <v>1.25</v>
       </c>
-      <c r="H26" s="0" t="n">
+      <c r="H26" s="1" t="n">
         <f aca="false">F26*G26</f>
         <v>7.5</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="H27" s="0" t="n">
+      <c r="H27" s="1" t="n">
         <f aca="false">SUM(H4:H26)</f>
         <v>479.27</v>
       </c>
@@ -3128,144 +3132,144 @@
   <dimension ref="A1:B19"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <f aca="false">BOM!H9</f>
         <v>113.8</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="1" t="n">
         <f aca="false">BOM!H15</f>
         <v>29.88</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <f aca="false">BOM!H23</f>
         <v>86.94</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="1" t="n">
         <f aca="false">BOM!H30</f>
         <v>23.63</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="1" t="n">
         <f aca="false">BOM!H36</f>
         <v>209.55</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="1" t="n">
         <f aca="false">BOM!H45</f>
         <v>163.75</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9" s="1" t="n">
         <f aca="false">BOM!H51</f>
         <v>21.49</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B10" s="0" t="n">
+      <c r="B10" s="1" t="n">
         <f aca="false">BOM!H59</f>
         <v>46.16</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B11" s="0" t="n">
+      <c r="B11" s="1" t="n">
         <f aca="false">BOM!H71</f>
-        <v>288.43</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+        <v>293.43</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B12" s="0" t="n">
+      <c r="B12" s="1" t="n">
         <f aca="false">BOM!H83</f>
         <v>217.95</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="B14" s="0" t="n">
+      <c r="B14" s="1" t="n">
         <f aca="false">BOM!H85</f>
-        <v>1201.58</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+        <v>1206.58</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="B15" s="0" t="n">
+      <c r="B15" s="1" t="n">
         <f aca="false">BOM!H86</f>
         <v>-39.6</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B16" s="0" t="n">
+      <c r="B16" s="1" t="n">
         <f aca="false">BOM!H87</f>
-        <v>1161.98</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+        <v>1166.98</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B18" s="0" t="n">
+      <c r="B18" s="1" t="n">
         <f aca="false">'Already Acquired'!H27</f>
         <v>479.27</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B19" s="0" t="n">
+      <c r="B19" s="1" t="n">
         <f aca="false">B16+B18</f>
-        <v>1641.25</v>
+        <v>1646.25</v>
       </c>
     </row>
   </sheetData>

--- a/Documentation/WYVERN_E4_BOM_Active.xlsx
+++ b/Documentation/WYVERN_E4_BOM_Active.xlsx
@@ -312,7 +312,7 @@
     <t xml:space="preserve">RP2350B flight computer board</t>
   </si>
   <si>
-    <t xml:space="preserve">DFM-reviewed Gerber submission (soldermask/silkscreen/SMT placement flags addressed). $200 total for 3 fabricated boards (updated 2026-08-10, was $195); one of the three is earmarked for the ground servo TVC test stand rather than flight/spare use.</t>
+    <t xml:space="preserve">DFM-reviewed Gerber submission (soldermask/silkscreen/SMT placement flags addressed). $207.01 total for 3 fabricated boards (updated 2026-08-11, was $200); one of the three is earmarked for the ground servo TVC test stand rather than flight/spare use.</t>
   </si>
   <si>
     <t xml:space="preserve">eMagTech F-F servo extension cable 10cm (10-pk)</t>
@@ -1969,11 +1969,11 @@
         <v>3</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>66.6666666666667</v>
+        <v>69.0033333333333</v>
       </c>
       <c r="H63" s="1" t="n">
         <f aca="false">F63*G63</f>
-        <v>200</v>
+        <v>207.01</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="H71" s="1" t="n">
         <f aca="false">SUM(H63:H70)</f>
-        <v>293.43</v>
+        <v>300.44</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="H85" s="1" t="n">
         <f aca="false">H9+H15+H23+H30+H36+H45+H51+H59+H71+H83</f>
-        <v>1206.58</v>
+        <v>1213.59</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="H87" s="1" t="n">
         <f aca="false">H85+H86</f>
-        <v>1166.98</v>
+        <v>1173.99</v>
       </c>
     </row>
   </sheetData>
@@ -3215,7 +3215,7 @@
       </c>
       <c r="B11" s="1" t="n">
         <f aca="false">BOM!H71</f>
-        <v>293.43</v>
+        <v>300.44</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="B14" s="1" t="n">
         <f aca="false">BOM!H85</f>
-        <v>1206.58</v>
+        <v>1213.59</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="B16" s="1" t="n">
         <f aca="false">BOM!H87</f>
-        <v>1166.98</v>
+        <v>1173.99</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="B19" s="1" t="n">
         <f aca="false">B16+B18</f>
-        <v>1646.25</v>
+        <v>1653.26</v>
       </c>
     </row>
   </sheetData>

--- a/Documentation/WYVERN_E4_BOM_Active.xlsx
+++ b/Documentation/WYVERN_E4_BOM_Active.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="205">
   <si>
-    <t xml:space="preserve">WYVERN-E - Active Procurement BOM (only items actually being bought)</t>
+    <t xml:space="preserve">GTR70E WYVERN - Active Procurement BOM (only items actually being bought)</t>
   </si>
   <si>
     <t xml:space="preserve">Trimmed copy of WYVERN_E4_BOM.xlsx, 2026-08-09f. Fully regenerated - adds HANGLIFE heat-set insert assortment (M2-M6, 345pc, $19.99) to Section 7, confirmed in the live Amazon cart. Contains ONLY line items with a real, nonzero cost confirmed in one of the live carts (Amazon/Adafruit/Estes/Bambu) or the custom PCB fab order. The master WYVERN_E4_BOM.xlsx remains the full historical record (including items still needed but not yet in a cart, e.g. the F15-4 flight motor and E16-4 commissioning motors - see that file before assuming procurement is complete).</t>
@@ -303,7 +303,7 @@
     <t xml:space="preserve">9. Custom PCB + 2026-08-09 cart items</t>
   </si>
   <si>
-    <t xml:space="preserve">Custom PCB fabrication (JLCPCB) - WYVERN-E flight computer, 3 boards</t>
+    <t xml:space="preserve">Custom PCB fabrication (JLCPCB) - GTR70E WYVERN flight computer, 3 boards</t>
   </si>
   <si>
     <t xml:space="preserve">JLCPCB</t>
@@ -312,7 +312,7 @@
     <t xml:space="preserve">RP2350B flight computer board</t>
   </si>
   <si>
-    <t xml:space="preserve">DFM-reviewed Gerber submission (soldermask/silkscreen/SMT placement flags addressed). $207.01 total for 3 fabricated boards (updated 2026-08-11, was $200); one of the three is earmarked for the ground servo TVC test stand rather than flight/spare use.</t>
+    <t xml:space="preserve">DFM-reviewed Gerber submission (soldermask/silkscreen/SMT placement flags addressed). $231.72 total for 3 fabricated boards (updated 2026-08-12, was $207.01) -- board grew from Ø61mm to Ø62mm and gained parts (65 components vs 61) to fit the larger SS-12D10-G5 switch; one of the three is earmarked for the ground servo TVC test stand rather than flight/spare use.</t>
   </si>
   <si>
     <t xml:space="preserve">eMagTech F-F servo extension cable 10cm (10-pk)</t>
@@ -624,7 +624,7 @@
     <t xml:space="preserve">Total already paid</t>
   </si>
   <si>
-    <t xml:space="preserve">WYVERN-E - Active Procurement Summary</t>
+    <t xml:space="preserve">GTR70E WYVERN - Active Procurement Summary</t>
   </si>
   <si>
     <t xml:space="preserve">Gross total (this round)</t>
@@ -1969,11 +1969,11 @@
         <v>3</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>69.0033333333333</v>
+        <v>77.24</v>
       </c>
       <c r="H63" s="1" t="n">
         <f aca="false">F63*G63</f>
-        <v>207.01</v>
+        <v>231.72</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="H71" s="1" t="n">
         <f aca="false">SUM(H63:H70)</f>
-        <v>300.44</v>
+        <v>325.15</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="H85" s="1" t="n">
         <f aca="false">H9+H15+H23+H30+H36+H45+H51+H59+H71+H83</f>
-        <v>1213.59</v>
+        <v>1238.3</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="H87" s="1" t="n">
         <f aca="false">H85+H86</f>
-        <v>1173.99</v>
+        <v>1198.7</v>
       </c>
     </row>
   </sheetData>
@@ -3215,7 +3215,7 @@
       </c>
       <c r="B11" s="1" t="n">
         <f aca="false">BOM!H71</f>
-        <v>300.44</v>
+        <v>325.15</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="B14" s="1" t="n">
         <f aca="false">BOM!H85</f>
-        <v>1213.59</v>
+        <v>1238.3</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="B16" s="1" t="n">
         <f aca="false">BOM!H87</f>
-        <v>1173.99</v>
+        <v>1198.7</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="B19" s="1" t="n">
         <f aca="false">B16+B18</f>
-        <v>1653.26</v>
+        <v>1677.97</v>
       </c>
     </row>
   </sheetData>
